--- a/practice/answers/q054.xlsx
+++ b/practice/answers/q054.xlsx
@@ -70146,7 +70146,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>(c) Each fraction is the share of yields to the right of that threshold, so the drops between them trace the same shape a histogram shows: the fall from 58% above 60 to 24% above 70 and 4% above 80 says most of the distribution sits between 50 and 70, exactly where a histogram's tall bars would be.</t>

--- a/practice/answers/q054.xlsx
+++ b/practice/answers/q054.xlsx
@@ -17,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -46,12 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,17 +65,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -70094,23 +70093,23 @@
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;40")</f>
         <v/>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;50")</f>
         <v/>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;60")</f>
         <v/>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;70")</f>
         <v/>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;80")</f>
         <v/>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <f>COUNTIF(Data!$F$2:$F$2399,"&gt;90")</f>
         <v/>
       </c>
@@ -70121,33 +70120,33 @@
           <t>Fraction of all rows (c)</t>
         </is>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <f>B2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <f>C2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <f>D2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <f>E2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <f>F2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <f>G2/COUNT(Data!$F$2:$F$2399)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>(c) Each fraction is the share of yields to the right of that threshold, so the drops between them trace the same shape a histogram shows: the fall from 58% above 60 to 24% above 70 and 4% above 80 says most of the distribution sits between 50 and 70, exactly where a histogram's tall bars would be.</t>
         </is>
@@ -70161,21 +70160,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Part (a)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Part (b)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Part (c)</t>
         </is>
